--- a/results/monthly_investor_report_2026-07-03.xlsx
+++ b/results/monthly_investor_report_2026-07-03.xlsx
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1023,19 +1023,19 @@
         <v>12757.11168923382</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1259383002873109</v>
+        <v>0.1259383002873111</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1606.608962717493</v>
+        <v>1606.608962717495</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>449.8123509647807</v>
+        <v>449.8123509647808</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>373.1666787300279</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.910596481506183</v>
+        <v>1.910596481506187</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1058567831986978</v>
+        <v>0.1058567831986977</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10585.67831986978</v>
+        <v>10585.67831986977</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.1047501473143974</v>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.06951830094919656</v>
+        <v>0.06951830094919655</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>6951.830094919656</v>
+        <v>6951.830094919655</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0319463736658787</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05901418175367707</v>
+        <v>0.05901418175367706</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>5901.418175367707</v>
@@ -1155,7 +1155,7 @@
         <v>40.80921186599804</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>36.51765369294939</v>
+        <v>36.51765369294938</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>0.1979746325938461</v>
@@ -1257,7 +1257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1457,19 +1457,19 @@
         <v>0.0618301731244848</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.1259383002873109</v>
+        <v>0.1259383002873111</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.2830390713974848</v>
+        <v>0.2830390713974846</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>424.2011541632316</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>449.8123509647807</v>
+        <v>449.8123509647808</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>512.5741090232953</v>
+        <v>512.5741090232951</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>373.1666787300279</v>
@@ -1682,7 +1682,7 @@
         <v>73.75</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.1195457879117688</v>
+        <v>-0.1195457879117687</v>
       </c>
       <c r="F12" s="19" t="n">
         <v>-0.0525384894872815</v>
@@ -1691,7 +1691,7 @@
         <v>0.05159344410234</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>64.93349814150704</v>
+        <v>64.93349814150706</v>
       </c>
       <c r="I12" s="18" t="n">
         <v>69.87528640031299</v>
@@ -1700,7 +1700,7 @@
         <v>77.55501650254757</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>64.93349814150704</v>
+        <v>64.93349814150706</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>0.004366982061861</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1062296048253292</v>
+        <v>0.1062296048253293</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>36.01196952636552</v>
@@ -1859,7 +1859,7 @@
         <v>-0.0056061959533879</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.1633018392220255</v>
+        <v>0.1633018392220254</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>181.012467304781</v>
@@ -1868,7 +1868,7 @@
         <v>188.5370713165358</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>220.562035816727</v>
+        <v>220.5620358167269</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>180.1200057983398</v>
@@ -1919,7 +1919,7 @@
         <v>0.0827585226318214</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>36.51765369294939</v>
+        <v>36.51765369294938</v>
       </c>
       <c r="I16" s="15" t="n">
         <v>40.80921186599804</v>
@@ -1928,7 +1928,7 @@
         <v>43.41861510537765</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>36.51765369294939</v>
+        <v>36.51765369294938</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
@@ -1976,13 +1976,13 @@
         <v>0.0625387106897197</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>103.3044372525922</v>
+        <v>103.3044372525923</v>
       </c>
       <c r="I17" s="21" t="n">
         <v>108.9707404116317</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>113.9041465433271</v>
+        <v>113.9041465433272</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>101.8399971008301</v>
@@ -2168,7 +2168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2279,7 +2279,7 @@
         <v>0.0329578488985884</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.1259383002873109</v>
+        <v>0.1259383002873111</v>
       </c>
     </row>
     <row r="5">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="J5" s="16" t="n">
-        <v>0.0224280868678006</v>
+        <v>0.0224280868678007</v>
       </c>
       <c r="K5" s="16" t="n">
         <v>0.211966460056985</v>
@@ -2520,7 +2520,7 @@
         <v>0.0308880308880308</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.057843565416608</v>
+        <v>0.0578435654166078</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>-0.07217851387470781</v>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0083681530871555</v>
+        <v>-0.0083681530871556</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>-0.0181253230935878</v>
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.4413204787850318</v>
+        <v>0.4413204787850315</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.6781684227851839</v>
+        <v>0.6781684227851834</v>
       </c>
       <c r="H12" s="16" t="n">
         <v>-0.2000140581789575</v>
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0064875307482625</v>
+        <v>-0.0064875307482624</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.0028063182233972</v>
+        <v>0.0028063182233974</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1166666348775227</v>
+        <v>0.1166666348775229</v>
       </c>
       <c r="H13" s="22" t="n">
         <v>-0.0013946075335394</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0262733290323232</v>
+        <v>0.0262733290323233</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>0.0121672257670984</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="J17" s="27" t="n">
-        <v>0.0218716122937669</v>
+        <v>0.0218716122937668</v>
       </c>
       <c r="K17" s="27" t="n">
         <v>0.0270714525721503</v>
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="E18" s="27" t="n">
-        <v>-0.0502369957512588</v>
+        <v>-0.0502369957512587</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>-0.0956679224870062</v>
+        <v>-0.09566792248700599</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>-0.044804618772834</v>
+        <v>-0.0448046187728339</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>-0.0867375485681951</v>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.027371838733298</v>
+        <v>0.0273718387332981</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -2950,7 +2950,7 @@
         <v>-0.0547403900411772</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.1683217225612643</v>
+        <v>-0.1683217225612644</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>-0.09388789028605229</v>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0217198916869541</v>
+        <v>0.021719891686954</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -3000,7 +3000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,7 +3119,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3495,7 +3495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3572,7 +3572,7 @@
         <v>338.4805471272794</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3602,7 +3602,7 @@
         <v>844.8417266280685</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3632,7 +3632,7 @@
         <v>-170.1874413355963</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3662,7 +3662,7 @@
         <v>-764.8350642277655</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3692,7 +3692,7 @@
         <v>-94416.71969714283</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3716,13 +3716,13 @@
         <v>40.09999847412109</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.005949471431804132</v>
+        <v>-0.005949471431804354</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-4231.310311300098</v>
+        <v>-4231.310311300214</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3752,7 +3752,7 @@
         <v>74.00308946839505</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3782,7 +3782,7 @@
         <v>-456.3221797124534</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3812,7 +3812,7 @@
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0.0520943075470665</v>

--- a/results/monthly_investor_report_2026-07-03.xlsx
+++ b/results/monthly_investor_report_2026-07-03.xlsx
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1257,7 +1257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2168,7 +2168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3000,7 +3000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,7 +3119,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3495,7 +3495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3572,7 +3572,7 @@
         <v>338.4805471272794</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3602,7 +3602,7 @@
         <v>844.8417266280685</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3632,7 +3632,7 @@
         <v>-170.1874413355963</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3662,7 +3662,7 @@
         <v>-764.8350642277655</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3692,7 +3692,7 @@
         <v>-94416.71969714283</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3722,7 +3722,7 @@
         <v>-4231.310311300214</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3752,7 +3752,7 @@
         <v>74.00308946839505</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3782,7 +3782,7 @@
         <v>-456.3221797124534</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3812,7 +3812,7 @@
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0.0520943075470665</v>

--- a/results/monthly_investor_report_2026-07-03.xlsx
+++ b/results/monthly_investor_report_2026-07-03.xlsx
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -974,25 +974,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1380396172060904</v>
+        <v>0.1380396116533548</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13803.96172060904</v>
+        <v>13803.96116533548</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.211966460056985</v>
+        <v>0.2119663640262494</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2925.976900679626</v>
+        <v>2925.97545737571</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>404.796797659033</v>
+        <v>404.7967655847673</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>317.3</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.239329201139705</v>
+        <v>4.239327280524994</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1275711168923382</v>
+        <v>0.1275711214916294</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>12757.11168923382</v>
+        <v>12757.11214916294</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1259383002873111</v>
+        <v>0.1259383002873109</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1606.608962717495</v>
+        <v>1606.609020640185</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>449.8123509647808</v>
+        <v>449.8123509647807</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>373.1666787300279</v>
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1058567831986977</v>
+        <v>0.1058567503448248</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10585.67831986977</v>
+        <v>10585.67503448248</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.1047501473143974</v>
+        <v>0.1047500099709655</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>1108.851363429182</v>
+        <v>1108.84956541144</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>333.6345444889481</v>
+        <v>333.6345030112316</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>285.1645786331716</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.879046790671904</v>
+        <v>1.879044326954746</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.06951830094919655</v>
+        <v>0.06951830345552337</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>6951.830094919655</v>
+        <v>6951.830345552337</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0319463736658787</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>222.0857618740043</v>
+        <v>222.0857698808096</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>137.7648408843948</v>
@@ -1117,7 +1117,7 @@
         <v>126.5130091330145</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.6103973750054179</v>
+        <v>0.6103973750054204</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05901418175367706</v>
+        <v>0.05901421305466755</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5901.418175367707</v>
+        <v>5901.421305466755</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0176861201711677</v>
+        <v>0.0176862670340702</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>104.3731910298665</v>
+        <v>104.3741130890362</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>40.80921186599804</v>
+        <v>40.80921775520021</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>36.51765369294938</v>
+        <v>36.51765090818546</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.1979746325938461</v>
+        <v>0.1979761226473516</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1457,19 +1457,19 @@
         <v>0.0618301731244848</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.1259383002873111</v>
+        <v>0.1259383002873109</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.2830390713974846</v>
+        <v>0.2830390713974848</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>424.2011541632316</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>449.8123509647808</v>
+        <v>449.8123509647807</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>512.5741090232951</v>
+        <v>512.5741090232953</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>373.1666787300279</v>
@@ -1511,22 +1511,22 @@
         <v>334</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.0457252883240006</v>
+        <v>0.0457252439987692</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.211966460056985</v>
+        <v>0.2119663640262494</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.3728564655733453</v>
+        <v>0.3728564122007715</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>349.2722463002162</v>
+        <v>349.2722314955889</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>404.796797659033</v>
+        <v>404.7967655847673</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>458.5340595014973</v>
+        <v>458.5340416750577</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>317.3</v>
@@ -1571,19 +1571,19 @@
         <v>-0.0194805194805194</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.1047501473143974</v>
+        <v>0.1047500099709655</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.1307691594971161</v>
+        <v>0.1307690576798095</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>296.1168831168831</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>333.6345444889481</v>
+        <v>333.6345030112316</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>341.4922861681291</v>
+        <v>341.4922554193025</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>285.1645786331716</v>
@@ -1628,19 +1628,19 @@
         <v>-0.0174048288175393</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.0036970289786339</v>
+        <v>-0.0036968005684216</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.1185391429973565</v>
+        <v>0.1185386588107133</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>350.7864761121385</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>355.6801606546277</v>
+        <v>355.6802421970735</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>399.3184740500563</v>
+        <v>399.3183011954247</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>339.15</v>
@@ -1682,25 +1682,25 @@
         <v>73.75</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.1195457879117687</v>
+        <v>-0.1195457879117688</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-0.0525384894872815</v>
+        <v>-0.0525383720373842</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.05159344410234</v>
+        <v>0.0515933378844173</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>64.93349814150706</v>
+        <v>64.93349814150704</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>69.87528640031299</v>
+        <v>69.87529506224291</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>77.55501650254757</v>
+        <v>77.55500866897577</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>64.93349814150706</v>
+        <v>64.93349814150704</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>0.004366982061861</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1062296048253293</v>
+        <v>0.1062296237000928</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>36.01196952636552</v>
@@ -1754,7 +1754,7 @@
         <v>38.18603311775468</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>42.05885008185074</v>
+        <v>42.05885079946926</v>
       </c>
       <c r="K13" s="21" t="n">
         <v>35.62858599261265</v>
@@ -1796,22 +1796,22 @@
         <v>133.5</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-0.0374467634999697</v>
+        <v>-0.0374466031122178</v>
       </c>
       <c r="F14" s="16" t="n">
         <v>0.0319463736658787</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.10818310737263</v>
+        <v>0.1081830165120092</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>128.5008570727541</v>
+        <v>128.5008784845189</v>
       </c>
       <c r="I14" s="15" t="n">
         <v>137.7648408843948</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>147.9424448342461</v>
+        <v>147.9424327043532</v>
       </c>
       <c r="K14" s="15" t="n">
         <v>126.5130091330145</v>
@@ -1853,22 +1853,22 @@
         <v>189.6000061035156</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>-0.0452929246956146</v>
+        <v>-0.0452929265798762</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>-0.0056061959533879</v>
+        <v>-0.005606274347556</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.1633018392220254</v>
+        <v>0.1633017563777966</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>181.012467304781</v>
+        <v>181.012466947525</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>188.5370713165358</v>
+        <v>188.537056453001</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>220.5620358167269</v>
+        <v>220.5620201094607</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>180.1200057983398</v>
@@ -1910,25 +1910,25 @@
         <v>40.09999847412109</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-0.08933528472534991</v>
+        <v>-0.089335354170837</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.0176861201711677</v>
+        <v>0.0176862670340702</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.0827585226318214</v>
+        <v>0.0827586281845227</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>36.51765369294938</v>
+        <v>36.51765090818546</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>40.80921186599804</v>
+        <v>40.80921775520021</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>43.41861510537765</v>
+        <v>43.41861933804081</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>36.51765369294938</v>
+        <v>36.51765090818546</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
@@ -1970,19 +1970,19 @@
         <v>-0.036339177299891</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>0.0165181297928999</v>
+        <v>0.0165180940172871</v>
       </c>
       <c r="G17" s="22" t="n">
         <v>0.0625387106897197</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>103.3044372525923</v>
+        <v>103.3044372525922</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>108.9707404116317</v>
+        <v>108.9707365764861</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>113.9041465433272</v>
+        <v>113.9041465433271</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>101.8399971008301</v>
@@ -2024,25 +2024,25 @@
         <v>248.1999969482422</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.0501087082729111</v>
+        <v>-0.0501087049018857</v>
       </c>
       <c r="F18" s="25" t="n">
-        <v>-0.0049330944485646</v>
+        <v>-0.004933032871861</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>0.0825054415792305</v>
+        <v>0.082505387163645</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>235.7630157078253</v>
+        <v>235.7630165445138</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>246.9756029211631</v>
+        <v>246.9756182045007</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>268.6778472964206</v>
+        <v>268.6778337904724</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>235.7630157078253</v>
+        <v>235.7630165445138</v>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
@@ -2081,25 +2081,25 @@
         <v>94.5</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.1036949211912278</v>
+        <v>-0.1036948476951217</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>-0.0265262577132464</v>
+        <v>-0.0265261865666126</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>0.0283369659971981</v>
+        <v>0.0283370297099155</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>84.70082994742897</v>
+        <v>84.700836892811</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>91.99326864609822</v>
+        <v>91.99327536945511</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>97.17784328673523</v>
+        <v>97.17784930758701</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>84.70082994742897</v>
+        <v>84.700836892811</v>
       </c>
       <c r="L19" s="23" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0329578488985884</v>
+        <v>0.0329578488985883</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.1259383002873111</v>
+        <v>0.1259383002873109</v>
       </c>
     </row>
     <row r="5">
@@ -2322,7 +2322,7 @@
         <v>0.0224280868678007</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>0.211966460056985</v>
+        <v>0.2119663640262494</v>
       </c>
     </row>
     <row r="6">
@@ -2365,7 +2365,7 @@
         <v>0.0278732141834907</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.1047501473143974</v>
+        <v>0.1047500099709655</v>
       </c>
     </row>
     <row r="7">
@@ -2408,7 +2408,7 @@
         <v>0.0199673156767437</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>-0.0036970289786339</v>
+        <v>-0.0036968005684216</v>
       </c>
     </row>
     <row r="8">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="J8" s="19" t="n">
-        <v>0.0317317702632586</v>
+        <v>0.0317317702632585</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>-0.0525384894872815</v>
+        <v>-0.0525383720373842</v>
       </c>
     </row>
     <row r="9">
@@ -2520,7 +2520,7 @@
         <v>0.0308880308880308</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.0578435654166078</v>
+        <v>0.057843565416608</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>-0.07217851387470781</v>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.026168505119796</v>
+        <v>0.0261685051197959</v>
       </c>
       <c r="K10" s="16" t="n">
         <v>0.0319463736658787</v>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0083681530871556</v>
+        <v>-0.0083681530871555</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>-0.0181253230935878</v>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="J11" s="19" t="n">
-        <v>0.0216342637490465</v>
+        <v>0.0216342637490466</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>-0.0056061959533879</v>
+        <v>-0.005606274347556</v>
       </c>
     </row>
     <row r="12">
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.4413204787850315</v>
+        <v>0.4413204787850318</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.6781684227851834</v>
+        <v>0.6781684227851839</v>
       </c>
       <c r="H12" s="16" t="n">
         <v>-0.2000140581789575</v>
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="J12" s="16" t="n">
-        <v>0.0276553695056337</v>
+        <v>0.0276553695056338</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>0.0176861201711677</v>
+        <v>0.0176862670340702</v>
       </c>
     </row>
     <row r="13">
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0064875307482624</v>
+        <v>-0.0064875307482625</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.0028063182233974</v>
+        <v>0.0028063182233972</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1166666348775229</v>
+        <v>0.1166666348775227</v>
       </c>
       <c r="H13" s="22" t="n">
         <v>-0.0013946075335394</v>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="J13" s="22" t="n">
-        <v>0.0234179516127443</v>
+        <v>0.0234179516127442</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>0.0165181297928999</v>
+        <v>0.0165180940172871</v>
       </c>
     </row>
     <row r="14">
@@ -2709,7 +2709,7 @@
         <v>0.0227948736710902</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>-0.0049330944485646</v>
+        <v>-0.004933032871861</v>
       </c>
     </row>
     <row r="15">
@@ -2752,7 +2752,7 @@
         <v>0.0257945186668304</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>-0.0265262577132464</v>
+        <v>-0.0265261865666126</v>
       </c>
     </row>
     <row r="16">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0262733290323233</v>
+        <v>0.0262733290323232</v>
       </c>
       <c r="K16" s="27" t="n">
-        <v>0.0121672257670984</v>
+        <v>0.0121672262735507</v>
       </c>
     </row>
     <row r="17">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="J17" s="27" t="n">
-        <v>0.0218716122937668</v>
+        <v>0.0218716122937669</v>
       </c>
       <c r="K17" s="27" t="n">
         <v>0.0270714525721503</v>
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="E18" s="27" t="n">
-        <v>-0.0502369957512587</v>
+        <v>-0.0502369957512588</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>-0.09566792248700599</v>
+        <v>-0.0956679224870062</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>-0.0448046187728339</v>
+        <v>-0.044804618772834</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>-0.0867375485681951</v>
@@ -2881,7 +2881,7 @@
         <v>0.0183815906397974</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.0759494774088542</v>
+        <v>0.0759492964836558</v>
       </c>
     </row>
     <row r="19">
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.0273718387332981</v>
+        <v>0.027371838733298</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -2950,7 +2950,7 @@
         <v>-0.0547403900411772</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.1683217225612644</v>
+        <v>-0.1683217225612643</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>-0.09388789028605229</v>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.021719891686954</v>
+        <v>0.0217198916869541</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -3000,7 +3000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,7 +3119,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14417.900390625</v>
+        <v>14424.5</v>
       </c>
     </row>
     <row r="5">
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12639.74602539062</v>
+        <v>12656.86702636719</v>
       </c>
     </row>
     <row r="6">
@@ -3495,7 +3495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3572,7 +3572,7 @@
         <v>338.4805471272794</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3602,7 +3602,7 @@
         <v>844.8417266280685</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3632,7 +3632,7 @@
         <v>-170.1874413355963</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3662,7 +3662,7 @@
         <v>-764.8350642277655</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3692,7 +3692,7 @@
         <v>-94416.71969714283</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3716,13 +3716,13 @@
         <v>40.09999847412109</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.005949471431804354</v>
+        <v>-0.005949471431804132</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-4231.310311300214</v>
+        <v>-4231.310311300098</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3752,7 +3752,7 @@
         <v>74.00308946839505</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3782,7 +3782,7 @@
         <v>-456.3221797124534</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3812,7 +3812,7 @@
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0.0520943075470665</v>
